--- a/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>140</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.2521</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-74.6396</v>
-      </c>
-      <c r="I2" t="n">
-        <v>263</v>
-      </c>
-      <c r="J2" t="n">
-        <v>12</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.2521</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-74.6396</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>652</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.2459</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-74.63420000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>57</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.2459</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-74.6342</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>31515 RAFAEL GASTELUA / RAFAEL GASTELUA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.2511351161024</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-74.64006523008371</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2009</v>
-      </c>
-      <c r="J4" t="n">
-        <v>124</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.2511351161024</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-74.6400652300837</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>30001-54</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.255549</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-74.645752</v>
-      </c>
-      <c r="I5" t="n">
-        <v>582</v>
-      </c>
-      <c r="J5" t="n">
-        <v>24</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.255549</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-74.645752</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>30632 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.249108</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-74.634692</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1192</v>
-      </c>
-      <c r="J6" t="n">
-        <v>59</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.249108</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-74.634692</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>JOSE OLAYA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.2589423654031</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-74.6384903471717</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1228</v>
-      </c>
-      <c r="J7" t="n">
-        <v>68</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.2589423654031</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-74.6384903471717</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>31834</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.245239</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-74.639223</v>
-      </c>
-      <c r="I8" t="n">
-        <v>251</v>
-      </c>
-      <c r="J8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.245239</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-74.639223</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>FRANCISCO IRAZOLA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.2528165560722</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-74.6431408564349</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1614</v>
-      </c>
-      <c r="J9" t="n">
-        <v>106</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.2528165560722</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-74.6431408564349</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1614</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>COLEGIO ADVENTISTA SATIPO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.250608</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-74.63629400000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>168</v>
-      </c>
-      <c r="J10" t="n">
-        <v>18</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.250608</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-74.636294</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.25305</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-74.63825</v>
-      </c>
-      <c r="I11" t="n">
-        <v>253</v>
-      </c>
-      <c r="J11" t="n">
-        <v>23</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.25305</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-74.63825</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.24925</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-74.63838</v>
-      </c>
-      <c r="I12" t="n">
-        <v>185</v>
-      </c>
-      <c r="J12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.24925</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-74.63838</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>GENERAL RAFAEL HOYOS RUBIO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.290402</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-74.54319099999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>280</v>
-      </c>
-      <c r="J13" t="n">
-        <v>23</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.290402</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-74.543191</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>246</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.42875</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-74.491032</v>
-      </c>
-      <c r="I14" t="n">
-        <v>305</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.42875</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-74.491032</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>SAN MARTIN</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.430407</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-74.49124999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>993</v>
-      </c>
-      <c r="J15" t="n">
-        <v>54</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.430407</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-74.49125</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>30638 JOSE GALVEZ / JOSE GALVEZ</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.210243</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-74.660347</v>
-      </c>
-      <c r="I16" t="n">
-        <v>986</v>
-      </c>
-      <c r="J16" t="n">
-        <v>50</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.210243</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-74.660347</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>31463 / 31463 SAN JORGE</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.2114</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-74.6237</v>
-      </c>
-      <c r="I17" t="n">
-        <v>502</v>
-      </c>
-      <c r="J17" t="n">
-        <v>29</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.2114</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-74.6237</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>CRAYON'S</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.258175462098</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-74.643997341664</v>
-      </c>
-      <c r="I18" t="n">
-        <v>206</v>
-      </c>
-      <c r="J18" t="n">
-        <v>14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.258175462098</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-74.643997341664</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>EL BUEN SAMARITANO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.25366</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-74.63994</v>
-      </c>
-      <c r="I19" t="n">
-        <v>157</v>
-      </c>
-      <c r="J19" t="n">
-        <v>17</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.25366</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-74.63994</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>EMANUEL</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.25644</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-74.624</v>
-      </c>
-      <c r="I20" t="n">
-        <v>511</v>
-      </c>
-      <c r="J20" t="n">
-        <v>25</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.25644</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-74.624</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>239346</t>
+          <t>239997</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>FRANCISCO IRAZOLA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.2521</t>
+          <t>-11.2528165560722</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.6396</t>
+          <t>-74.6431408564349</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -563,42 +563,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>239407</t>
+          <t>239346</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.2459</t>
+          <t>-11.2521</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.6342</t>
+          <t>-74.6396</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>239469</t>
+          <t>241108</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30001-54</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.255549</t>
+          <t>-11.42875</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.645752</t>
+          <t>-74.491032</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>239539</t>
+          <t>527498</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30632 DIVINO NIÑO JESUS</t>
+          <t>CRAYON'S</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.249108</t>
+          <t>-11.258175462098</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.634692</t>
+          <t>-74.643997341664</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>239723</t>
+          <t>239860</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JOSE OLAYA</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.2589423654031</t>
+          <t>-11.245239</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.6384903471717</t>
+          <t>-74.639223</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>239860</t>
+          <t>240180</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31834</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.245239</t>
+          <t>-11.24925</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.639223</t>
+          <t>-74.63838</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>185</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>239997</t>
+          <t>537534</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FRANCISCO IRAZOLA</t>
+          <t>EL BUEN SAMARITANO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.2528165560722</t>
+          <t>-11.25366</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.6431408564349</t>
+          <t>-74.63994</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>157</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>240180</t>
+          <t>240769</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>GENERAL RAFAEL HOYOS RUBIO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.24925</t>
+          <t>-11.290402</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-74.63838</t>
+          <t>-74.543191</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>240769</t>
+          <t>239469</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GENERAL RAFAEL HOYOS RUBIO</t>
+          <t>30001-54</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.290402</t>
+          <t>-11.255549</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.543191</t>
+          <t>-74.645752</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>582</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>241108</t>
+          <t>716837</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>EMANUEL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.42875</t>
+          <t>-11.25644</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.491032</t>
+          <t>-74.624</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>511</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>241815</t>
+          <t>242693</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>31463 / 31463 SAN JORGE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.430407</t>
+          <t>-11.2114</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.49125</t>
+          <t>-74.6237</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>502</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,42 +1369,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>242476</t>
+          <t>239407</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30638 JOSE GALVEZ / JOSE GALVEZ</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.210243</t>
+          <t>-11.2459</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.660347</t>
+          <t>-74.6342</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>242693</t>
+          <t>242476</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31463 / 31463 SAN JORGE</t>
+          <t>30638 JOSE GALVEZ / JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.2114</t>
+          <t>-11.210243</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-74.6237</t>
+          <t>-74.660347</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>986</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>527498</t>
+          <t>241815</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRAYON'S</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.258175462098</t>
+          <t>-11.430407</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-74.643997341664</t>
+          <t>-74.49125</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>993</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>537534</t>
+          <t>239539</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EL BUEN SAMARITANO</t>
+          <t>30632 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.25366</t>
+          <t>-11.249108</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-74.63994</t>
+          <t>-74.634692</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>716837</t>
+          <t>239723</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EMANUEL</t>
+          <t>JOSE OLAYA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.25644</t>
+          <t>-11.2589423654031</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-74.624</t>
+          <t>-74.6384903471717</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>239997</t>
+          <t>902189</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FRANCISCO IRAZOLA</t>
+          <t>CRISTO CENTRICO ELOHIM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.2528165560722</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-74.6431408564349</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>-11.260107</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-74.637272</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>239346</t>
+          <t>716837</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>EMANUEL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.2521</t>
+          <t>511</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-74.6396</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-11.25644</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-74.624</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>239445</t>
+          <t>612769</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31515 RAFAEL GASTELUA / RAFAEL GASTELUA</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.2511351161024</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-74.6400652300837</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>-11.26418</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>-74.64357</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>241108</t>
+          <t>612750</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.42875</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-74.491032</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-11.249683</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-74.633283</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>527498</t>
+          <t>537534</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CRAYON'S</t>
+          <t>EL BUEN SAMARITANO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.258175462098</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-74.643997341664</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-11.25366</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-74.63994</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>239860</t>
+          <t>527498</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31834</t>
+          <t>CRAYON'S</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.245239</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-74.639223</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-11.258175462098</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.643997341664</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>240180</t>
+          <t>242693</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALBERT EINSTEIN</t>
+          <t>31463 / 31463 SAN JORGE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.24925</t>
+          <t>502</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-74.63838</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>-11.2114</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-74.6237</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>537534</t>
+          <t>242476</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EL BUEN SAMARITANO</t>
+          <t>30638 JOSE GALVEZ / JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.25366</t>
+          <t>986</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-74.63994</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>-11.210243</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-74.660347</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>240137</t>
+          <t>241815</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COLEGIO ADVENTISTA SATIPO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.250608</t>
+          <t>993</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-74.636294</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>-11.430407</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-74.49125</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>240156</t>
+          <t>241108</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.25305</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-74.63825</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>-11.42875</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-74.491032</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1131,22 +1131,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>-11.290402</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>-74.543191</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>239469</t>
+          <t>240180</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30001-54</t>
+          <t>ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.255549</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-74.645752</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>-11.24925</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-74.63838</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>716837</t>
+          <t>240156</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EMANUEL</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.25644</t>
+          <t>253</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-74.624</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>-11.25305</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-74.63825</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>242693</t>
+          <t>240137</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31463 / 31463 SAN JORGE</t>
+          <t>COLEGIO ADVENTISTA SATIPO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.2114</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-74.6237</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>-11.250608</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-74.636294</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>239407</t>
+          <t>239997</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>FRANCISCO IRAZOLA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.2459</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-74.6342</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-11.2528165560722</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-74.6431408564349</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>242476</t>
+          <t>239860</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30638 JOSE GALVEZ / JOSE GALVEZ</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.210243</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-74.660347</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>-11.245239</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-74.639223</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>241815</t>
+          <t>239723</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>JOSE OLAYA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.430407</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-74.49125</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>-11.2589423654031</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-74.6384903471717</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1565,22 +1565,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>-11.249108</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>-74.634692</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>239723</t>
+          <t>239469</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JOSE OLAYA</t>
+          <t>30001-54</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.2589423654031</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-74.6384903471717</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>-11.255549</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-74.645752</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>612750</t>
+          <t>239445</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>31515 RAFAEL GASTELUA / RAFAEL GASTELUA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.249683</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-74.633283</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-11.2511351161024</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-74.6400652300837</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,42 +1741,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>902189</t>
+          <t>239407</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CRISTO CENTRICO ELOHIM</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.260107</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-74.637272</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>-11.2459</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-74.6342</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>612769</t>
+          <t>239346</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.26418</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-74.64357</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-11.2521</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-74.6396</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
+++ b/ZonasEscolares/excels/JUNIN-SATIPO-SATIPO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
